--- a/registros_de_series.xlsx
+++ b/registros_de_series.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
   <si>
     <t>ID</t>
   </si>
@@ -38,31 +38,10 @@
     <t>Fecha de Creación</t>
   </si>
   <si>
-    <t>BRENDY YOSELY ZAPATA TORRES</t>
-  </si>
-  <si>
-    <t>CRIS-TAURO</t>
-  </si>
-  <si>
-    <t>sdav</t>
-  </si>
-  <si>
-    <t>LUSTRADORA</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>EMER RODRIGO YARLEQUE ZAPATA</t>
-  </si>
-  <si>
-    <t>hola</t>
-  </si>
-  <si>
-    <t>COMPAÑIA FOOD RETAIL S.A.C.</t>
-  </si>
-  <si>
-    <t>ASPIRADORA</t>
+    <t>["84932","84933","84934"]</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
   </si>
 </sst>
 </file>
@@ -413,7 +392,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="true" style="0"/>
@@ -452,299 +431,15 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14">
-        <v>17</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
